--- a/SOL/MELI/MELI_Conceptos_2026.xlsx
+++ b/SOL/MELI/MELI_Conceptos_2026.xlsx
@@ -20,10 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$ARS] #,##0.00;[Red]-[$ARS] #,##0.00;–"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -124,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,8 +148,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O35"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1482,20 +1486,6 @@
           <t>INDICADORES (NO SE SUMAN NUEVAMENTE)</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="16" t="n"/>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="16" t="n"/>
-      <c r="J30" s="16" t="n"/>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
-      <c r="M30" s="16" t="n"/>
-      <c r="N30" s="16" t="n"/>
-      <c r="O30" s="16" t="n"/>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="17" t="inlineStr">
@@ -1665,21 +1655,106 @@
         <v/>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1"/>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>CAR ALLOWANCE DESDE JULIO (+12%)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="n"/>
+      <c r="D34" s="22" t="n"/>
+      <c r="E34" s="22" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n">
+        <v>349440</v>
+      </c>
+      <c r="J34" s="22" t="n">
+        <v>349440</v>
+      </c>
+      <c r="K34" s="22" t="n">
+        <v>349440</v>
+      </c>
+      <c r="L34" s="22" t="n">
+        <v>349440</v>
+      </c>
+      <c r="M34" s="22" t="n">
+        <v>349440</v>
+      </c>
+      <c r="N34" s="22" t="n">
+        <v>349440</v>
+      </c>
+      <c r="O34" s="22">
+        <f>SUM(C34:N34)</f>
+        <v/>
+      </c>
+    </row>
     <row r="35" ht="35" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
-        <is>
-          <t>Notas: importes de descuentos se muestran positivos; devoluciones/ajustes que reducen descuentos se muestran negativos. Abril consolida sueldo y bono. Junio consolida sueldo y SAC.</t>
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>BRUTO TOTAL DESDE JULIO</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+      <c r="H35" s="7" t="n"/>
+      <c r="I35" s="7">
+        <f>I33+I34</f>
+        <v/>
+      </c>
+      <c r="J35" s="7">
+        <f>J33+J34</f>
+        <v/>
+      </c>
+      <c r="K35" s="7">
+        <f>K33+K34</f>
+        <v/>
+      </c>
+      <c r="L35" s="7">
+        <f>L33+L34</f>
+        <v/>
+      </c>
+      <c r="M35" s="7">
+        <f>M33+M34</f>
+        <v/>
+      </c>
+      <c r="N35" s="7">
+        <f>N33+N34</f>
+        <v/>
+      </c>
+      <c r="O35" s="7">
+        <f>SUM(C35:N35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="35" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Notas: importes de descuentos se muestran positivos; devoluciones/ajustes que reducen descuentos se muestran negativos. Abril consolida sueldo y bono. Junio consolida sueldo y SAC. Desde julio, básico y car allowance aumentan 12%.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:O27"/>
   <mergeCells count="4">
-    <mergeCell ref="A35:O35"/>
+    <mergeCell ref="A2:O2"/>
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A37:O37"/>
     <mergeCell ref="A30:O30"/>
-    <mergeCell ref="A2:O2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -1758,7 +1833,7 @@
           <t>Sueldo</t>
         </is>
       </c>
-      <c r="C2" s="20" t="n">
+      <c r="C2" s="24" t="n">
         <v>46054</v>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -1791,7 +1866,7 @@
           <t>Sueldo</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="24" t="n">
         <v>46082</v>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -1824,7 +1899,7 @@
           <t>Sueldo + retroactivo</t>
         </is>
       </c>
-      <c r="C4" s="20" t="n">
+      <c r="C4" s="24" t="n">
         <v>46113</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1857,7 +1932,7 @@
           <t>Bono</t>
         </is>
       </c>
-      <c r="C5" s="20" t="n">
+      <c r="C5" s="24" t="n">
         <v>46118</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1890,7 +1965,7 @@
           <t>Sueldo + vacaciones</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="24" t="n">
         <v>46143</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1923,7 +1998,7 @@
           <t>Sueldo</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="24" t="n">
         <v>46174</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1956,7 +2031,7 @@
           <t>SAC</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="24" t="n">
         <v>46196</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1989,7 +2064,7 @@
           <t>Sueldo</t>
         </is>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="24" t="n">
         <v>46204</v>
       </c>
       <c r="D9" s="5" t="inlineStr">

--- a/SOL/MELI/MELI_Conceptos_2026.xlsx
+++ b/SOL/MELI/MELI_Conceptos_2026.xlsx
@@ -7,12 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Conceptos por mes" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Fuentes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ingresos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Conceptos por mes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Fuentes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Conceptos por mes'!$A$4:$O$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Fuentes'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conceptos por mes'!$A$4:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fuentes'!$A$1:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -20,9 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="[$ARS] #,##0.00;[Red]-[$ARS] #,##0.00;–"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="166" formatCode="[$ARS] #,##0.00"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -123,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -155,6 +157,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -232,6 +241,21 @@
 </file>
 
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Cursor</author>
+  </authors>
+  <commentList>
+    <comment ref="B12" authorId="0" shapeId="0">
+      <text>
+        <t>Importe informado: ARS 8.784.847,44. No se proporcionó recibo en esta actualización.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Cursor</author>
@@ -535,6 +559,267 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SOL — Ingresos 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ingresos mensuales de Sol. Los importes se registran según el mes informado y no se mezclan con gastos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>Mes</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>MELI</t>
+        </is>
+      </c>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Otros ingresos</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>TOTAL INGRESOS</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Comentario</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Enero</t>
+        </is>
+      </c>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26">
+        <f>SUM(B5:C5)</f>
+        <v/>
+      </c>
+      <c r="E5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Febrero</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="26">
+        <f>SUM(B6:C6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Marzo</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="26">
+        <f>SUM(B7:C7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Abril</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="26">
+        <f>SUM(B8:C8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="26" t="n"/>
+      <c r="D9" s="26">
+        <f>SUM(B9:C9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Junio</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26">
+        <f>SUM(B10:C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26">
+        <f>SUM(B11:C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Agosto</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="n">
+        <v>8784847.439999999</v>
+      </c>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28">
+        <f>SUM(B12:C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>MELI · ingreso neto agosto informado por usuario</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Septiembre</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26">
+        <f>SUM(B13:C13)</f>
+        <v/>
+      </c>
+      <c r="E13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Octubre</t>
+        </is>
+      </c>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="26">
+        <f>SUM(B14:C14)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Noviembre</t>
+        </is>
+      </c>
+      <c r="B15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="26">
+        <f>SUM(B15:C15)</f>
+        <v/>
+      </c>
+      <c r="E15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Diciembre</t>
+        </is>
+      </c>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26">
+        <f>SUM(B16:C16)</f>
+        <v/>
+      </c>
+      <c r="E16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL AÑO</t>
+        </is>
+      </c>
+      <c r="B17" s="29">
+        <f>SUM(B5:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="29">
+        <f>SUM(C5:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="29">
+        <f>SUM(D5:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="11" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1751,9 +2036,9 @@
   </sheetData>
   <autoFilter ref="A4:O27"/>
   <mergeCells count="4">
-    <mergeCell ref="A2:O2"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A37:O37"/>
+    <mergeCell ref="A2:O2"/>
     <mergeCell ref="A30:O30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1761,7 +2046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/SOL/MELI/MELI_Conceptos_2026.xlsx
+++ b/SOL/MELI/MELI_Conceptos_2026.xlsx
@@ -248,7 +248,7 @@
   <commentList>
     <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>Importe informado: ARS 8.784.847,44. No se proporcionó recibo en esta actualización.</t>
+        <t>ARS 8.784.847,44: sueldo del período julio 2026, cobrado en agosto 2026.</t>
       </text>
     </comment>
   </commentList>
@@ -559,14 +559,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -579,14 +580,15 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ingresos mensuales de Sol. Los importes se registran según el mes informado y no se mezclan con gastos.</t>
-        </is>
-      </c>
-    </row>
+          <t>Ingresos por mes de cobro, identificando por separado el período salarial. No se mezclan con gastos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>Mes</t>
+          <t>Mes de cobro</t>
         </is>
       </c>
       <c r="B4" s="25" t="inlineStr">
@@ -605,6 +607,11 @@
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t>Período salarial</t>
+        </is>
+      </c>
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Comentario</t>
         </is>
@@ -623,6 +630,7 @@
         <v/>
       </c>
       <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -637,6 +645,7 @@
         <v/>
       </c>
       <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -651,6 +660,7 @@
         <v/>
       </c>
       <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -665,6 +675,7 @@
         <v/>
       </c>
       <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -679,6 +690,7 @@
         <v/>
       </c>
       <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -693,6 +705,7 @@
         <v/>
       </c>
       <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -707,6 +720,7 @@
         <v/>
       </c>
       <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="27" t="inlineStr">
@@ -724,7 +738,12 @@
       </c>
       <c r="E12" s="27" t="inlineStr">
         <is>
-          <t>MELI · ingreso neto agosto informado por usuario</t>
+          <t>Julio 2026</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="inlineStr">
+        <is>
+          <t>MELI · sueldo neto cobrado en agosto</t>
         </is>
       </c>
     </row>
@@ -741,6 +760,7 @@
         <v/>
       </c>
       <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -755,6 +775,7 @@
         <v/>
       </c>
       <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -769,6 +790,7 @@
         <v/>
       </c>
       <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -783,6 +805,7 @@
         <v/>
       </c>
       <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -803,11 +826,12 @@
         <v/>
       </c>
       <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/SOL/MELI/MELI_Conceptos_2026.xlsx
+++ b/SOL/MELI/MELI_Conceptos_2026.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conceptos por mes'!$A$4:$O$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fuentes'!$A$1:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Fuentes'!$A$1:$J$10</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -164,6 +164,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -248,7 +250,7 @@
   <commentList>
     <comment ref="B12" authorId="0" shapeId="0">
       <text>
-        <t>ARS 8.784.847,44: sueldo del período julio 2026, cobrado en agosto 2026.</t>
+        <t>Recibo MELI: período julio 2026, pago 01/08/2026, neto ARS 8.784.847,44.</t>
       </text>
     </comment>
   </commentList>
@@ -584,7 +586,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
@@ -743,7 +744,7 @@
       </c>
       <c r="F12" s="27" t="inlineStr">
         <is>
-          <t>MELI · sueldo neto cobrado en agosto</t>
+          <t>MELI · sueldo neto julio cobrado 01/08/2026 · verificado con recibo</t>
         </is>
       </c>
     </row>
@@ -985,7 +986,9 @@
       <c r="H5" s="6" t="n">
         <v>11305702</v>
       </c>
-      <c r="I5" s="7" t="n"/>
+      <c r="I5" s="30" t="n">
+        <v>12662386</v>
+      </c>
       <c r="J5" s="7" t="n"/>
       <c r="K5" s="7" t="n"/>
       <c r="L5" s="7" t="n"/>
@@ -1025,7 +1028,9 @@
       <c r="H6" s="6" t="n">
         <v>312000</v>
       </c>
-      <c r="I6" s="7" t="n"/>
+      <c r="I6" s="30" t="n">
+        <v>360000</v>
+      </c>
       <c r="J6" s="7" t="n"/>
       <c r="K6" s="7" t="n"/>
       <c r="L6" s="7" t="n"/>
@@ -1458,7 +1463,9 @@
       <c r="H20" s="6" t="n">
         <v>728417.64</v>
       </c>
-      <c r="I20" s="7" t="n"/>
+      <c r="I20" s="30" t="n">
+        <v>496052.42</v>
+      </c>
       <c r="J20" s="7" t="n"/>
       <c r="K20" s="7" t="n"/>
       <c r="L20" s="7" t="n"/>
@@ -1498,7 +1505,9 @@
       <c r="H21" s="6" t="n">
         <v>198659.36</v>
       </c>
-      <c r="I21" s="7" t="n"/>
+      <c r="I21" s="30" t="n">
+        <v>135287.02</v>
+      </c>
       <c r="J21" s="7" t="n"/>
       <c r="K21" s="7" t="n"/>
       <c r="L21" s="7" t="n"/>
@@ -1538,7 +1547,9 @@
       <c r="H22" s="6" t="n">
         <v>198659.36</v>
       </c>
-      <c r="I22" s="7" t="n"/>
+      <c r="I22" s="30" t="n">
+        <v>135287.02</v>
+      </c>
       <c r="J22" s="7" t="n"/>
       <c r="K22" s="7" t="n"/>
       <c r="L22" s="7" t="n"/>
@@ -1578,7 +1589,9 @@
       <c r="H23" s="6" t="n">
         <v>3944533.32</v>
       </c>
-      <c r="I23" s="7" t="n"/>
+      <c r="I23" s="30" t="n">
+        <v>3445112.1</v>
+      </c>
       <c r="J23" s="7" t="n"/>
       <c r="K23" s="7" t="n"/>
       <c r="L23" s="7" t="n"/>
@@ -1648,7 +1661,9 @@
       <c r="H25" s="6" t="n">
         <v>23400</v>
       </c>
-      <c r="I25" s="7" t="n"/>
+      <c r="I25" s="30" t="n">
+        <v>25800</v>
+      </c>
       <c r="J25" s="7" t="n"/>
       <c r="K25" s="7" t="n"/>
       <c r="L25" s="7" t="n"/>
@@ -1932,7 +1947,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>BÁSICO VIGENTE DESDE JULIO (+12%)</t>
+          <t>BÁSICO VIGENTE DESDE JULIO (RECIBO)</t>
         </is>
       </c>
       <c r="C33" s="6" t="n"/>
@@ -1942,22 +1957,22 @@
       <c r="G33" s="6" t="n"/>
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="6" t="n">
-        <v>12662387</v>
+        <v>12662386</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>12662387</v>
+        <v>12662386</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>12662387</v>
+        <v>12662386</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>12662387</v>
+        <v>12662386</v>
       </c>
       <c r="M33" s="6" t="n">
-        <v>12662387</v>
+        <v>12662386</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>12662387</v>
+        <v>12662386</v>
       </c>
       <c r="O33" s="6">
         <f>SUM(C33:N33)</f>
@@ -1972,7 +1987,7 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>CAR ALLOWANCE DESDE JULIO (+12%)</t>
+          <t>CAR ALLOWANCE DESDE JULIO (RECIBO)</t>
         </is>
       </c>
       <c r="C34" s="22" t="n"/>
@@ -1982,22 +1997,22 @@
       <c r="G34" s="22" t="n"/>
       <c r="H34" s="22" t="n"/>
       <c r="I34" s="22" t="n">
-        <v>349440</v>
+        <v>360000</v>
       </c>
       <c r="J34" s="22" t="n">
-        <v>349440</v>
+        <v>360000</v>
       </c>
       <c r="K34" s="22" t="n">
-        <v>349440</v>
+        <v>360000</v>
       </c>
       <c r="L34" s="22" t="n">
-        <v>349440</v>
+        <v>360000</v>
       </c>
       <c r="M34" s="22" t="n">
-        <v>349440</v>
+        <v>360000</v>
       </c>
       <c r="N34" s="22" t="n">
-        <v>349440</v>
+        <v>360000</v>
       </c>
       <c r="O34" s="22">
         <f>SUM(C34:N34)</f>
@@ -2012,7 +2027,7 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>BRUTO TOTAL DESDE JULIO</t>
+          <t>BRUTO TOTAL DESDE JULIO (RECIBO)</t>
         </is>
       </c>
       <c r="C35" s="7" t="n"/>
@@ -2053,7 +2068,7 @@
     <row r="37" ht="35" customHeight="1">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>Notas: importes de descuentos se muestran positivos; devoluciones/ajustes que reducen descuentos se muestran negativos. Abril consolida sueldo y bono. Junio consolida sueldo y SAC. Desde julio, básico y car allowance aumentan 12%.</t>
+          <t>Notas: valores enero–junio extraídos de recibos previos. Julio: recibo MELI pagado 01/08/2026; básico ARS 12.662.386, beneficio auto ARS 360.000, bruto ARS 13.022.386.</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2087,6 +2102,8 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2130,6 +2147,16 @@
           <t>Estado</t>
         </is>
       </c>
+      <c r="I1" s="19" t="inlineStr">
+        <is>
+          <t>Contribuciones empleador</t>
+        </is>
+      </c>
+      <c r="J1" s="19" t="inlineStr">
+        <is>
+          <t>Costo total empleador</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -2395,8 +2422,47 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Julio</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Sueldo</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>46235</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Tu Recibo.pdf</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>13022386</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>4237538.56</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>8784847.439999999</v>
+      </c>
+      <c r="H10" s="31">
+        <f>ROUND(E10-F10-G10,2)</f>
+        <v/>
+      </c>
+      <c r="I10" s="31" t="n">
+        <v>3191487.53</v>
+      </c>
+      <c r="J10" s="31" t="n">
+        <v>16213873.53</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H9"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>